--- a/activity/M03A08/M03A08_PasoViaModelacion1D.xlsx
+++ b/activity/M03A08/M03A08_PasoViaModelacion1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64603C0-6CCF-4AD6-9D1B-E828DA976C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7916A5-5B3A-4575-8D59-E22400E390C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -251,7 +251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -421,6 +421,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -428,18 +452,46 @@
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -451,7 +503,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -496,9 +548,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -526,36 +575,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -564,9 +583,6 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -593,6 +609,54 @@
     </xf>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -710,7 +774,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="65000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2011,40 +2075,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2052,15 +2116,15 @@
       <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="28">
         <v>5</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <f>Detalle!C13*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="22">
+      <c r="E5" s="30"/>
+      <c r="F5" s="21">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
       </c>
@@ -2069,15 +2133,15 @@
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="28">
         <v>5</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <f>Detalle!F13*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="22">
+      <c r="E6" s="30"/>
+      <c r="F6" s="21">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
       </c>
@@ -2086,15 +2150,15 @@
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="28">
         <v>5</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <f>Detalle!I13*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="22">
+      <c r="E7" s="30"/>
+      <c r="F7" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2103,15 +2167,15 @@
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="28">
         <v>5</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <f>Detalle!L13*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="22">
+      <c r="E8" s="30"/>
+      <c r="F8" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2120,15 +2184,15 @@
       <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="28">
         <v>5</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <f>Detalle!O13*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="22">
+      <c r="E9" s="30"/>
+      <c r="F9" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2137,15 +2201,15 @@
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="28">
         <v>5</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <f>Detalle!R13*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="22">
+      <c r="E10" s="30"/>
+      <c r="F10" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2154,15 +2218,15 @@
       <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="28">
         <v>5</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <f>Detalle!U13*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="22">
+      <c r="E11" s="30"/>
+      <c r="F11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2171,15 +2235,15 @@
       <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="28">
         <v>5</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <f>Detalle!X13*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="22">
+      <c r="E12" s="30"/>
+      <c r="F12" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2188,15 +2252,15 @@
       <c r="B13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="28">
         <v>5</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <f>Detalle!AA13*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="42"/>
-      <c r="F13" s="22">
+      <c r="E13" s="30"/>
+      <c r="F13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2205,15 +2269,15 @@
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="28">
         <v>5</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <f>Detalle!AD13*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="42"/>
-      <c r="F14" s="22">
+      <c r="E14" s="30"/>
+      <c r="F14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2222,15 +2286,15 @@
       <c r="B15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="28">
         <v>5</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <f>Detalle!AG13*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="22">
+      <c r="E15" s="30"/>
+      <c r="F15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2239,15 +2303,15 @@
       <c r="B16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="28">
         <v>5</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <f>Detalle!AJ13*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="22">
+      <c r="E16" s="30"/>
+      <c r="F16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2256,57 +2320,57 @@
       <c r="B17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="28">
         <v>5</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <f>Detalle!AM13*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="42"/>
-      <c r="F17" s="22">
+      <c r="E17" s="30"/>
+      <c r="F17" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="29">
         <v>5</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="25">
         <f>Detalle!AP13*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="37">
+      <c r="E18" s="31"/>
+      <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="38" t="str">
+      <c r="B19" s="37" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A08 en GitHub.</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
@@ -2365,7 +2429,7 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
-      <c r="B1" s="24" t="str">
+      <c r="B1" s="23" t="str">
         <f>Calificacion!B2</f>
         <v>Calificación: 3.8. Modelación de pasos de vía en modelos hidráulicos 1D</v>
       </c>
@@ -2400,220 +2464,220 @@
     </row>
     <row r="2" spans="1:44" s="12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="11"/>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="27" t="str">
+      <c r="C2" s="40" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="27" t="str">
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="40" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="27" t="str">
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="40" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="27" t="str">
+      <c r="J2" s="41"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="40" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="27" t="str">
+      <c r="M2" s="41"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="40" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="27" t="str">
+      <c r="P2" s="41"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="40" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="28"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="27" t="str">
+      <c r="S2" s="41"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="40" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="28"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="27" t="str">
+      <c r="V2" s="41"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="40" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="27" t="str">
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="40" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="27" t="str">
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="40" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="27" t="str">
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="40" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="27" t="str">
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="40" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="27" t="str">
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="42"/>
+      <c r="AM2" s="40" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="27" t="str">
+      <c r="AN2" s="41"/>
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="40" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="29"/>
+      <c r="AQ2" s="41"/>
+      <c r="AR2" s="42"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="34"/>
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="E3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16" t="s">
+      <c r="H3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="16" t="s">
+      <c r="K3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" s="16" t="s">
+      <c r="N3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="P3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="16" t="s">
+      <c r="Q3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="16" t="s">
+      <c r="T3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="V3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="W3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="X3" s="16" t="s">
+      <c r="W3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="Y3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AB3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="16" t="s">
+      <c r="AC3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AE3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="16" t="s">
+      <c r="AF3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AH3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
+      <c r="AI3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AK3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="16" t="s">
+      <c r="AL3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AO3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="16" t="s">
+      <c r="AO3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="AQ3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR3" s="17" t="s">
+      <c r="AR3" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2621,408 +2685,408 @@
       <c r="B4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="44">
-        <v>0</v>
-      </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="44">
-        <v>0</v>
-      </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44">
-        <v>0</v>
-      </c>
-      <c r="J4" s="45"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="44">
-        <v>0</v>
-      </c>
-      <c r="M4" s="45"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="44">
-        <v>0</v>
-      </c>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="44">
-        <v>0</v>
-      </c>
-      <c r="S4" s="45"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="44">
-        <v>0</v>
-      </c>
-      <c r="V4" s="45"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="45"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="45"/>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="45"/>
-      <c r="AI4" s="46"/>
-      <c r="AJ4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="45"/>
-      <c r="AL4" s="46"/>
-      <c r="AM4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="45"/>
-      <c r="AO4" s="46"/>
-      <c r="AP4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="45"/>
-      <c r="AR4" s="46"/>
+      <c r="C4" s="32">
+        <v>0</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="32">
+        <v>0</v>
+      </c>
+      <c r="G4" s="33"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="32">
+        <v>0</v>
+      </c>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="32">
+        <v>0</v>
+      </c>
+      <c r="M4" s="33"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="32">
+        <v>0</v>
+      </c>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="32">
+        <v>0</v>
+      </c>
+      <c r="S4" s="33"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="32">
+        <v>0</v>
+      </c>
+      <c r="V4" s="33"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="32">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="33"/>
+      <c r="AR4" s="34"/>
     </row>
     <row r="5" spans="1:44" ht="68.650000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="44"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="44"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="45"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="44"/>
-      <c r="AN5" s="45"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="44"/>
-      <c r="AQ5" s="45"/>
-      <c r="AR5" s="46"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="34"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="33"/>
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="32"/>
+      <c r="AN5" s="33"/>
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="32"/>
+      <c r="AQ5" s="33"/>
+      <c r="AR5" s="34"/>
     </row>
     <row r="6" spans="1:44" ht="81.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="45"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="45"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="44"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="46"/>
-      <c r="AD6" s="44"/>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="46"/>
-      <c r="AG6" s="44"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46"/>
-      <c r="AJ6" s="44"/>
-      <c r="AK6" s="45"/>
-      <c r="AL6" s="46"/>
-      <c r="AM6" s="44"/>
-      <c r="AN6" s="45"/>
-      <c r="AO6" s="46"/>
-      <c r="AP6" s="44"/>
-      <c r="AQ6" s="45"/>
-      <c r="AR6" s="46"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="33"/>
+      <c r="AI6" s="34"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="33"/>
+      <c r="AL6" s="34"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="33"/>
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="33"/>
+      <c r="AR6" s="34"/>
     </row>
     <row r="7" spans="1:44" ht="81.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="45"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="45"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="44"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46"/>
-      <c r="AJ7" s="44"/>
-      <c r="AK7" s="45"/>
-      <c r="AL7" s="46"/>
-      <c r="AM7" s="44"/>
-      <c r="AN7" s="45"/>
-      <c r="AO7" s="46"/>
-      <c r="AP7" s="44"/>
-      <c r="AQ7" s="45"/>
-      <c r="AR7" s="46"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="33"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="33"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="32"/>
+      <c r="AN7" s="33"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="33"/>
+      <c r="AR7" s="34"/>
     </row>
     <row r="8" spans="1:44" ht="94.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="46"/>
-      <c r="AD8" s="44"/>
-      <c r="AE8" s="45"/>
-      <c r="AF8" s="46"/>
-      <c r="AG8" s="44"/>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="46"/>
-      <c r="AJ8" s="44"/>
-      <c r="AK8" s="45"/>
-      <c r="AL8" s="46"/>
-      <c r="AM8" s="44"/>
-      <c r="AN8" s="45"/>
-      <c r="AO8" s="46"/>
-      <c r="AP8" s="44"/>
-      <c r="AQ8" s="45"/>
-      <c r="AR8" s="46"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="32"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="34"/>
+      <c r="AM8" s="32"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="32"/>
+      <c r="AQ8" s="33"/>
+      <c r="AR8" s="34"/>
     </row>
     <row r="9" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="44"/>
-      <c r="AE9" s="45"/>
-      <c r="AF9" s="46"/>
-      <c r="AG9" s="44"/>
-      <c r="AH9" s="45"/>
-      <c r="AI9" s="46"/>
-      <c r="AJ9" s="44"/>
-      <c r="AK9" s="45"/>
-      <c r="AL9" s="46"/>
-      <c r="AM9" s="44"/>
-      <c r="AN9" s="45"/>
-      <c r="AO9" s="46"/>
-      <c r="AP9" s="44"/>
-      <c r="AQ9" s="45"/>
-      <c r="AR9" s="46"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="33"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="32"/>
+      <c r="AK9" s="33"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="32"/>
+      <c r="AN9" s="33"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="32"/>
+      <c r="AQ9" s="33"/>
+      <c r="AR9" s="34"/>
     </row>
     <row r="10" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="46"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="46"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
-      <c r="AJ10" s="44"/>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="46"/>
-      <c r="AM10" s="44"/>
-      <c r="AN10" s="45"/>
-      <c r="AO10" s="46"/>
-      <c r="AP10" s="44"/>
-      <c r="AQ10" s="45"/>
-      <c r="AR10" s="46"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="34"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="34"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="33"/>
+      <c r="AI10" s="34"/>
+      <c r="AJ10" s="32"/>
+      <c r="AK10" s="33"/>
+      <c r="AL10" s="34"/>
+      <c r="AM10" s="32"/>
+      <c r="AN10" s="33"/>
+      <c r="AO10" s="34"/>
+      <c r="AP10" s="32"/>
+      <c r="AQ10" s="33"/>
+      <c r="AR10" s="34"/>
     </row>
     <row r="11" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B11" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="45"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="44"/>
-      <c r="AE11" s="45"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="44"/>
-      <c r="AH11" s="45"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="44"/>
-      <c r="AK11" s="45"/>
-      <c r="AL11" s="46"/>
-      <c r="AM11" s="44"/>
-      <c r="AN11" s="45"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="44"/>
-      <c r="AQ11" s="45"/>
-      <c r="AR11" s="46"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="34"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="32"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="32"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="32"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="34"/>
+      <c r="AJ11" s="32"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="32"/>
+      <c r="AN11" s="33"/>
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="32"/>
+      <c r="AQ11" s="33"/>
+      <c r="AR11" s="34"/>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B12" s="14"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="44"/>
       <c r="D12" s="45"/>
       <c r="E12" s="46"/>
@@ -3068,93 +3132,93 @@
     </row>
     <row r="13" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="48">
         <f>AVERAGE(C4:C12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="30">
+      <c r="D13" s="48"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="48">
         <f>AVERAGE(F4:F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="30">
+      <c r="G13" s="48"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="48">
         <f>AVERAGE(I4:I12)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="31"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="30">
+      <c r="J13" s="48"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="48">
         <f>AVERAGE(L4:L12)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="30">
+      <c r="M13" s="48"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="48">
         <f>AVERAGE(O4:O12)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="30">
+      <c r="P13" s="48"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="48">
         <f>AVERAGE(R4:R12)</f>
         <v>0</v>
       </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="30">
+      <c r="S13" s="48"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="48">
         <f>AVERAGE(U4:U12)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="31"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="30">
+      <c r="V13" s="48"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="48">
         <f>AVERAGE(X4:X12)</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="30">
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="48">
         <f>AVERAGE(AA4:AA12)</f>
         <v>0</v>
       </c>
-      <c r="AB13" s="31"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="30">
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="48">
         <f>AVERAGE(AD4:AD12)</f>
         <v>0</v>
       </c>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="32"/>
-      <c r="AG13" s="30">
+      <c r="AE13" s="48"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="48">
         <f>AVERAGE(AG4:AG12)</f>
         <v>0</v>
       </c>
-      <c r="AH13" s="31"/>
-      <c r="AI13" s="32"/>
-      <c r="AJ13" s="30">
+      <c r="AH13" s="48"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="48">
         <f>AVERAGE(AJ4:AJ12)</f>
         <v>0</v>
       </c>
-      <c r="AK13" s="31"/>
-      <c r="AL13" s="32"/>
-      <c r="AM13" s="30">
+      <c r="AK13" s="48"/>
+      <c r="AL13" s="49"/>
+      <c r="AM13" s="48">
         <f>AVERAGE(AM4:AM12)</f>
         <v>0</v>
       </c>
-      <c r="AN13" s="31"/>
-      <c r="AO13" s="32"/>
-      <c r="AP13" s="30">
+      <c r="AN13" s="48"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="48">
         <f>AVERAGE(AP4:AP12)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="31"/>
-      <c r="AR13" s="32"/>
+      <c r="AQ13" s="48"/>
+      <c r="AR13" s="49"/>
     </row>
     <row r="14" spans="1:44" s="11" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="3"/>
@@ -4778,19 +4842,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="AA13:AC13"/>
-    <mergeCell ref="AD13:AF13"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="R13:T13"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP13:AR13"/>
     <mergeCell ref="C2:E2"/>
@@ -4807,6 +4858,19 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="AA13:AC13"/>
+    <mergeCell ref="AD13:AF13"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="R13:T13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
